--- a/downloads/10.5281_zenodo.19682386/hbm4eu_alignedstudies.xlsx
+++ b/downloads/10.5281_zenodo.19682386/hbm4eu_alignedstudies.xlsx
@@ -749,18 +749,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="30.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="33.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="5.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="18.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="25.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="65.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -1227,18 +1215,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="31.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="34.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="5.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="25.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="72.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -1615,18 +1591,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="28.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="31.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="5.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="25.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="82.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
